--- a/backend/data/financials_by_company/002540.SZ.xlsx
+++ b/backend/data/financials_by_company/002540.SZ.xlsx
@@ -697,658 +697,658 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-1000196.069201</v>
+        <v>6416596.056409</v>
       </c>
       <c r="C2" t="n">
-        <v>0.078515</v>
+        <v>0.114798</v>
       </c>
       <c r="D2" t="n">
-        <v>793466472.1799999</v>
+        <v>649809520.8099999</v>
       </c>
       <c r="E2" t="n">
-        <v>-12738916.31</v>
+        <v>55894823.65</v>
       </c>
       <c r="F2" t="n">
-        <v>-12738916.31</v>
+        <v>55894823.65</v>
       </c>
       <c r="G2" t="n">
-        <v>462883318.15</v>
+        <v>458050652.75</v>
       </c>
       <c r="H2" t="n">
-        <v>227906764.32</v>
+        <v>183605452.41</v>
       </c>
       <c r="I2" t="n">
-        <v>6449921903.62</v>
+        <v>5146481841.89</v>
       </c>
       <c r="J2" t="n">
-        <v>780727555.87</v>
+        <v>705704344.46</v>
       </c>
       <c r="K2" t="n">
-        <v>552820791.55</v>
+        <v>522098892.05</v>
       </c>
       <c r="L2" t="n">
-        <v>-38167409.12</v>
+        <v>-1037816.52</v>
       </c>
       <c r="M2" t="n">
-        <v>50622421.85</v>
+        <v>4610238.8</v>
       </c>
       <c r="N2" t="n">
-        <v>13288920.72</v>
+        <v>4596607.21</v>
       </c>
       <c r="O2" t="n">
-        <v>474622038.390799</v>
+        <v>408572425.156409</v>
       </c>
       <c r="P2" t="n">
-        <v>462883318.15</v>
+        <v>458050652.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>6896201533.09</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>5581826013.99</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0</v>
+      </c>
       <c r="S2" t="n">
-        <v>508118676.87</v>
+        <v>514217216.9</v>
       </c>
       <c r="T2" t="n">
-        <v>1325174114</v>
+        <v>1239649940</v>
       </c>
       <c r="U2" t="n">
-        <v>1234355515</v>
+        <v>1239649940</v>
       </c>
       <c r="V2" t="n">
-        <v>0.3493</v>
+        <v>0.3695</v>
       </c>
       <c r="W2" t="n">
-        <v>0.375</v>
+        <v>0.3695</v>
       </c>
       <c r="X2" t="n">
-        <v>462883318.15</v>
+        <v>458050652.75</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>462883318.15</v>
+        <v>458050652.75</v>
       </c>
       <c r="AA2" t="n">
-        <v>115055.62</v>
+        <v>-31503.89</v>
       </c>
       <c r="AB2" t="n">
-        <v>462768262.53</v>
+        <v>458082156.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>462768262.53</v>
+        <v>458082156.64</v>
       </c>
       <c r="AD2" t="n">
-        <v>39430107.17</v>
+        <v>59406496.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>502198369.7</v>
+        <v>517488653.25</v>
       </c>
       <c r="AF2" t="n">
-        <v>-5920307.17</v>
+        <v>3271436.35</v>
       </c>
       <c r="AG2" t="n">
-        <v>-11652473.8</v>
+        <v>70044860.25</v>
       </c>
       <c r="AH2" t="n">
-        <v>-988935.61</v>
+        <v>-92591631.22</v>
       </c>
       <c r="AI2" t="n">
-        <v>9529278.470000001</v>
+        <v>21122611</v>
       </c>
       <c r="AJ2" t="n">
-        <v>3112130.94</v>
+        <v>1424159.97</v>
       </c>
       <c r="AK2" t="n">
-        <v>-38167409.12</v>
+        <v>-1037816.52</v>
       </c>
       <c r="AL2" t="n">
-        <v>833907.99</v>
+        <v>1024184.93</v>
       </c>
       <c r="AM2" t="n">
-        <v>50622421.85</v>
+        <v>4610238.8</v>
       </c>
       <c r="AN2" t="n">
-        <v>13288920.72</v>
+        <v>4596607.21</v>
       </c>
       <c r="AO2" t="n">
-        <v>536374572.52</v>
+        <v>434943014.14</v>
       </c>
       <c r="AP2" t="n">
-        <v>446279629.47</v>
+        <v>435344172.1</v>
       </c>
       <c r="AQ2" t="n">
-        <v>34821218.65</v>
+        <v>25376131.36</v>
       </c>
       <c r="AR2" t="n">
-        <v>7470405.27</v>
+        <v>7510870.78</v>
       </c>
       <c r="AS2" t="n">
-        <v>7424156.44</v>
+        <v>6817138.34</v>
       </c>
       <c r="AT2" t="n">
-        <v>46248.83</v>
+        <v>693732.4399999999</v>
       </c>
       <c r="AU2" t="n">
-        <v>251810066.45</v>
+        <v>204052804.75</v>
       </c>
       <c r="AV2" t="n">
-        <v>90029309.62</v>
+        <v>66082550.28</v>
       </c>
       <c r="AW2" t="n">
-        <v>9445778.68</v>
+        <v>9136909.23</v>
       </c>
       <c r="AX2" t="n">
-        <v>80583530.94</v>
-      </c>
-      <c r="AY2" t="inlineStr"/>
+        <v>56945641.05</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
       <c r="AZ2" t="n">
-        <v>982654201.99</v>
+        <v>870287186.24</v>
       </c>
       <c r="BA2" t="n">
-        <v>6449921903.62</v>
+        <v>5146481841.89</v>
       </c>
       <c r="BB2" t="n">
-        <v>7432576105.61</v>
+        <v>6016769028.13</v>
       </c>
       <c r="BC2" t="n">
-        <v>7432576105.61</v>
+        <v>6016769028.13</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-1775479.069542</v>
+        <v>29744704.593866</v>
       </c>
       <c r="C3" t="n">
-        <v>0.092269</v>
+        <v>0.117926</v>
       </c>
       <c r="D3" t="n">
-        <v>902783289.3099999</v>
+        <v>719298540.92</v>
       </c>
       <c r="E3" t="n">
-        <v>-19242503.44</v>
+        <v>252230994.62</v>
       </c>
       <c r="F3" t="n">
-        <v>-19242503.44</v>
+        <v>252230994.62</v>
       </c>
       <c r="G3" t="n">
-        <v>565370945.9</v>
+        <v>676128608.45</v>
       </c>
       <c r="H3" t="n">
-        <v>225198587.42</v>
+        <v>204432762.07</v>
       </c>
       <c r="I3" t="n">
-        <v>6047414155.15</v>
+        <v>5785224100.05</v>
       </c>
       <c r="J3" t="n">
-        <v>883540785.87</v>
+        <v>971529535.54</v>
       </c>
       <c r="K3" t="n">
-        <v>658342198.45</v>
+        <v>767096773.47</v>
       </c>
       <c r="L3" t="n">
-        <v>-9979779.77</v>
+        <v>8555294.23</v>
       </c>
       <c r="M3" t="n">
-        <v>39390749.51</v>
+        <v>2047184.73</v>
       </c>
       <c r="N3" t="n">
-        <v>30369773.96</v>
+        <v>11355210.88</v>
       </c>
       <c r="O3" t="n">
-        <v>582837970.270458</v>
+        <v>453642318.423866</v>
       </c>
       <c r="P3" t="n">
-        <v>565370945.9</v>
+        <v>676128608.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>6487175296.79</v>
+        <v>6262599959.99</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>618227065.24</v>
+        <v>767010792.3200001</v>
       </c>
       <c r="T3" t="n">
-        <v>1299703324</v>
+        <v>1237877350</v>
       </c>
       <c r="U3" t="n">
-        <v>1223746636</v>
+        <v>1237877350</v>
       </c>
       <c r="V3" t="n">
-        <v>0.435</v>
+        <v>0.5462</v>
       </c>
       <c r="W3" t="n">
-        <v>0.462</v>
+        <v>0.5462</v>
       </c>
       <c r="X3" t="n">
-        <v>565370945.9</v>
+        <v>676128608.45</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>565370945.9</v>
+        <v>676128608.45</v>
       </c>
       <c r="AA3" t="n">
-        <v>3529287.59</v>
+        <v>1298598.2</v>
       </c>
       <c r="AB3" t="n">
-        <v>561841658.3099999</v>
+        <v>674830010.25</v>
       </c>
       <c r="AC3" t="n">
-        <v>561841658.3099999</v>
+        <v>674830010.25</v>
       </c>
       <c r="AD3" t="n">
-        <v>57109790.63</v>
+        <v>90219578.48999999</v>
       </c>
       <c r="AE3" t="n">
-        <v>618951448.9400001</v>
+        <v>765049588.74</v>
       </c>
       <c r="AF3" t="n">
-        <v>724383.7</v>
+        <v>-1961203.58</v>
       </c>
       <c r="AG3" t="n">
-        <v>-26460379.09</v>
+        <v>269467103.23</v>
       </c>
       <c r="AH3" t="n">
-        <v>1235848.75</v>
+        <v>-289947155.22</v>
       </c>
       <c r="AI3" t="n">
-        <v>23374090.61</v>
+        <v>15895709.83</v>
       </c>
       <c r="AJ3" t="n">
-        <v>1850439.73</v>
+        <v>4584342.16</v>
       </c>
       <c r="AK3" t="n">
-        <v>-9979779.77</v>
+        <v>8555294.23</v>
       </c>
       <c r="AL3" t="n">
-        <v>958804.22</v>
+        <v>752731.92</v>
       </c>
       <c r="AM3" t="n">
-        <v>39390749.51</v>
+        <v>2047184.73</v>
       </c>
       <c r="AN3" t="n">
-        <v>30369773.96</v>
+        <v>11355210.88</v>
       </c>
       <c r="AO3" t="n">
-        <v>623514083.15</v>
+        <v>466330521.59</v>
       </c>
       <c r="AP3" t="n">
-        <v>439761141.64</v>
+        <v>477375859.94</v>
       </c>
       <c r="AQ3" t="n">
-        <v>30445207.7</v>
+        <v>28459487.04</v>
       </c>
       <c r="AR3" t="n">
-        <v>11474645.2</v>
+        <v>7291820.51</v>
       </c>
       <c r="AS3" t="n">
-        <v>8828778.66</v>
+        <v>6736834.55</v>
       </c>
       <c r="AT3" t="n">
-        <v>2645866.54</v>
+        <v>554985.96</v>
       </c>
       <c r="AU3" t="n">
-        <v>247866800.65</v>
+        <v>225516172.67</v>
       </c>
       <c r="AV3" t="n">
-        <v>77571398.7</v>
+        <v>63994802.03</v>
       </c>
       <c r="AW3" t="n">
-        <v>12718784.06</v>
+        <v>7803615.29</v>
       </c>
       <c r="AX3" t="n">
-        <v>64852614.64</v>
+        <v>56191186.74</v>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="n">
-        <v>1063275224.79</v>
+        <v>943706381.53</v>
       </c>
       <c r="BA3" t="n">
-        <v>6047414155.15</v>
+        <v>5785224100.05</v>
       </c>
       <c r="BB3" t="n">
-        <v>7110689379.94</v>
+        <v>6728930481.58</v>
       </c>
       <c r="BC3" t="n">
-        <v>7110689379.94</v>
+        <v>6728930481.58</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>29744704.593866</v>
+        <v>-1775479.069542</v>
       </c>
       <c r="C4" t="n">
-        <v>0.117926</v>
+        <v>0.092269</v>
       </c>
       <c r="D4" t="n">
-        <v>719298540.92</v>
+        <v>902783289.3099999</v>
       </c>
       <c r="E4" t="n">
-        <v>252230994.62</v>
+        <v>-19242503.44</v>
       </c>
       <c r="F4" t="n">
-        <v>252230994.62</v>
+        <v>-19242503.44</v>
       </c>
       <c r="G4" t="n">
-        <v>676128608.45</v>
+        <v>565370945.9</v>
       </c>
       <c r="H4" t="n">
-        <v>204432762.07</v>
+        <v>225198587.42</v>
       </c>
       <c r="I4" t="n">
-        <v>5785224100.05</v>
+        <v>6047414155.15</v>
       </c>
       <c r="J4" t="n">
-        <v>971529535.54</v>
+        <v>883540785.87</v>
       </c>
       <c r="K4" t="n">
-        <v>767096773.47</v>
+        <v>658342198.45</v>
       </c>
       <c r="L4" t="n">
-        <v>8555294.23</v>
+        <v>-9979779.77</v>
       </c>
       <c r="M4" t="n">
-        <v>2047184.73</v>
+        <v>39390749.51</v>
       </c>
       <c r="N4" t="n">
-        <v>11355210.88</v>
+        <v>30369773.96</v>
       </c>
       <c r="O4" t="n">
-        <v>453642318.423866</v>
+        <v>582837970.270458</v>
       </c>
       <c r="P4" t="n">
-        <v>676128608.45</v>
+        <v>565370945.9</v>
       </c>
       <c r="Q4" t="n">
-        <v>6262599959.99</v>
+        <v>6487175296.79</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>767010792.3200001</v>
+        <v>618227065.24</v>
       </c>
       <c r="T4" t="n">
-        <v>1237877350</v>
+        <v>1299703324</v>
       </c>
       <c r="U4" t="n">
-        <v>1237877350</v>
+        <v>1223746636</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5462</v>
+        <v>0.435</v>
       </c>
       <c r="W4" t="n">
-        <v>0.5462</v>
+        <v>0.462</v>
       </c>
       <c r="X4" t="n">
-        <v>676128608.45</v>
+        <v>565370945.9</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>676128608.45</v>
+        <v>565370945.9</v>
       </c>
       <c r="AA4" t="n">
-        <v>1298598.2</v>
+        <v>3529287.59</v>
       </c>
       <c r="AB4" t="n">
-        <v>674830010.25</v>
+        <v>561841658.3099999</v>
       </c>
       <c r="AC4" t="n">
-        <v>674830010.25</v>
+        <v>561841658.3099999</v>
       </c>
       <c r="AD4" t="n">
-        <v>90219578.48999999</v>
+        <v>57109790.63</v>
       </c>
       <c r="AE4" t="n">
-        <v>765049588.74</v>
+        <v>618951448.9400001</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1961203.58</v>
+        <v>724383.7</v>
       </c>
       <c r="AG4" t="n">
-        <v>269467103.23</v>
+        <v>-26460379.09</v>
       </c>
       <c r="AH4" t="n">
-        <v>-289947155.22</v>
+        <v>1235848.75</v>
       </c>
       <c r="AI4" t="n">
-        <v>15895709.83</v>
+        <v>23374090.61</v>
       </c>
       <c r="AJ4" t="n">
-        <v>4584342.16</v>
+        <v>1850439.73</v>
       </c>
       <c r="AK4" t="n">
-        <v>8555294.23</v>
+        <v>-9979779.77</v>
       </c>
       <c r="AL4" t="n">
-        <v>752731.92</v>
+        <v>958804.22</v>
       </c>
       <c r="AM4" t="n">
-        <v>2047184.73</v>
+        <v>39390749.51</v>
       </c>
       <c r="AN4" t="n">
-        <v>11355210.88</v>
+        <v>30369773.96</v>
       </c>
       <c r="AO4" t="n">
-        <v>466330521.59</v>
+        <v>623514083.15</v>
       </c>
       <c r="AP4" t="n">
-        <v>477375859.94</v>
+        <v>439761141.64</v>
       </c>
       <c r="AQ4" t="n">
-        <v>28459487.04</v>
+        <v>30445207.7</v>
       </c>
       <c r="AR4" t="n">
-        <v>7291820.51</v>
+        <v>11474645.2</v>
       </c>
       <c r="AS4" t="n">
-        <v>6736834.55</v>
+        <v>8828778.66</v>
       </c>
       <c r="AT4" t="n">
-        <v>554985.96</v>
+        <v>2645866.54</v>
       </c>
       <c r="AU4" t="n">
-        <v>225516172.67</v>
+        <v>247866800.65</v>
       </c>
       <c r="AV4" t="n">
-        <v>63994802.03</v>
+        <v>77571398.7</v>
       </c>
       <c r="AW4" t="n">
-        <v>7803615.29</v>
+        <v>12718784.06</v>
       </c>
       <c r="AX4" t="n">
-        <v>56191186.74</v>
+        <v>64852614.64</v>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="n">
-        <v>943706381.53</v>
+        <v>1063275224.79</v>
       </c>
       <c r="BA4" t="n">
-        <v>5785224100.05</v>
+        <v>6047414155.15</v>
       </c>
       <c r="BB4" t="n">
-        <v>6728930481.58</v>
+        <v>7110689379.94</v>
       </c>
       <c r="BC4" t="n">
-        <v>6728930481.58</v>
+        <v>7110689379.94</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>6416596.056409</v>
+        <v>-1000196.069201</v>
       </c>
       <c r="C5" t="n">
-        <v>0.114798</v>
+        <v>0.078515</v>
       </c>
       <c r="D5" t="n">
-        <v>649809520.8099999</v>
+        <v>793466472.1799999</v>
       </c>
       <c r="E5" t="n">
-        <v>55894823.65</v>
+        <v>-12738916.31</v>
       </c>
       <c r="F5" t="n">
-        <v>55894823.65</v>
+        <v>-12738916.31</v>
       </c>
       <c r="G5" t="n">
-        <v>458050652.75</v>
+        <v>462883318.15</v>
       </c>
       <c r="H5" t="n">
-        <v>183605452.41</v>
+        <v>227906764.32</v>
       </c>
       <c r="I5" t="n">
-        <v>5146481841.89</v>
+        <v>6449921903.62</v>
       </c>
       <c r="J5" t="n">
-        <v>705704344.46</v>
+        <v>780727555.87</v>
       </c>
       <c r="K5" t="n">
-        <v>522098892.05</v>
+        <v>552820791.55</v>
       </c>
       <c r="L5" t="n">
-        <v>-1037816.52</v>
+        <v>-38167409.12</v>
       </c>
       <c r="M5" t="n">
-        <v>4610238.8</v>
+        <v>50622421.85</v>
       </c>
       <c r="N5" t="n">
-        <v>4596607.21</v>
+        <v>13288920.72</v>
       </c>
       <c r="O5" t="n">
-        <v>408572425.156409</v>
+        <v>474622038.390799</v>
       </c>
       <c r="P5" t="n">
-        <v>458050652.75</v>
+        <v>462883318.15</v>
       </c>
       <c r="Q5" t="n">
-        <v>5581826013.99</v>
-      </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
+        <v>6896201533.09</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>514217216.9</v>
+        <v>508118676.87</v>
       </c>
       <c r="T5" t="n">
-        <v>1239649940</v>
+        <v>1325174114</v>
       </c>
       <c r="U5" t="n">
-        <v>1239649940</v>
+        <v>1234355515</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3695</v>
+        <v>0.3493</v>
       </c>
       <c r="W5" t="n">
-        <v>0.3695</v>
+        <v>0.375</v>
       </c>
       <c r="X5" t="n">
-        <v>458050652.75</v>
+        <v>462883318.15</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>458050652.75</v>
+        <v>462883318.15</v>
       </c>
       <c r="AA5" t="n">
-        <v>-31503.89</v>
+        <v>115055.62</v>
       </c>
       <c r="AB5" t="n">
-        <v>458082156.64</v>
+        <v>462768262.53</v>
       </c>
       <c r="AC5" t="n">
-        <v>458082156.64</v>
+        <v>462768262.53</v>
       </c>
       <c r="AD5" t="n">
-        <v>59406496.61</v>
+        <v>39430107.17</v>
       </c>
       <c r="AE5" t="n">
-        <v>517488653.25</v>
+        <v>502198369.7</v>
       </c>
       <c r="AF5" t="n">
-        <v>3271436.35</v>
+        <v>-5920307.17</v>
       </c>
       <c r="AG5" t="n">
-        <v>70044860.25</v>
+        <v>-11652473.8</v>
       </c>
       <c r="AH5" t="n">
-        <v>-92591631.22</v>
+        <v>-988935.61</v>
       </c>
       <c r="AI5" t="n">
-        <v>21122611</v>
+        <v>9529278.470000001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1424159.97</v>
+        <v>3112130.94</v>
       </c>
       <c r="AK5" t="n">
-        <v>-1037816.52</v>
+        <v>-38167409.12</v>
       </c>
       <c r="AL5" t="n">
-        <v>1024184.93</v>
+        <v>833907.99</v>
       </c>
       <c r="AM5" t="n">
-        <v>4610238.8</v>
+        <v>50622421.85</v>
       </c>
       <c r="AN5" t="n">
-        <v>4596607.21</v>
+        <v>13288920.72</v>
       </c>
       <c r="AO5" t="n">
-        <v>434943014.14</v>
+        <v>536374572.52</v>
       </c>
       <c r="AP5" t="n">
-        <v>435344172.1</v>
+        <v>446279629.47</v>
       </c>
       <c r="AQ5" t="n">
-        <v>25376131.36</v>
+        <v>34821218.65</v>
       </c>
       <c r="AR5" t="n">
-        <v>7510870.78</v>
+        <v>7470405.27</v>
       </c>
       <c r="AS5" t="n">
-        <v>6817138.34</v>
+        <v>7424156.44</v>
       </c>
       <c r="AT5" t="n">
-        <v>693732.4399999999</v>
+        <v>46248.83</v>
       </c>
       <c r="AU5" t="n">
-        <v>204052804.75</v>
+        <v>251810066.45</v>
       </c>
       <c r="AV5" t="n">
-        <v>66082550.28</v>
+        <v>90029309.62</v>
       </c>
       <c r="AW5" t="n">
-        <v>9136909.23</v>
+        <v>9445778.68</v>
       </c>
       <c r="AX5" t="n">
-        <v>56945641.05</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>0</v>
-      </c>
+        <v>80583530.94</v>
+      </c>
+      <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="n">
-        <v>870287186.24</v>
+        <v>982654201.99</v>
       </c>
       <c r="BA5" t="n">
-        <v>5146481841.89</v>
+        <v>6449921903.62</v>
       </c>
       <c r="BB5" t="n">
-        <v>6016769028.13</v>
+        <v>7432576105.61</v>
       </c>
       <c r="BC5" t="n">
-        <v>6016769028.13</v>
+        <v>7432576105.61</v>
       </c>
     </row>
   </sheetData>
@@ -1754,134 +1754,132 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>1251285791</v>
+        <v>1270529500</v>
       </c>
       <c r="C2" t="n">
-        <v>1251285791</v>
-      </c>
-      <c r="D2" t="n">
-        <v>621436773.89</v>
-      </c>
+        <v>1270529500</v>
+      </c>
+      <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
-        <v>1461214780.51</v>
+        <v>229034062.35</v>
       </c>
       <c r="F2" t="n">
-        <v>5276507911.52</v>
+        <v>4784649943.41</v>
       </c>
       <c r="G2" t="n">
-        <v>7000047840.95</v>
+        <v>5217082848</v>
       </c>
       <c r="H2" t="n">
-        <v>3740882658.08</v>
+        <v>2922688018.25</v>
       </c>
       <c r="I2" t="n">
-        <v>5276507911.52</v>
+        <v>4784649943.41</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>3611419.54</v>
       </c>
       <c r="K2" t="n">
-        <v>5559671263.26</v>
+        <v>5015048365.73</v>
       </c>
       <c r="L2" t="n">
-        <v>6807321845.52</v>
+        <v>5045048365.73</v>
       </c>
       <c r="M2" t="n">
-        <v>5564507394.39</v>
+        <v>5023979869.62</v>
       </c>
       <c r="N2" t="n">
-        <v>4836131.13</v>
+        <v>8931503.890000001</v>
       </c>
       <c r="O2" t="n">
-        <v>5559671263.26</v>
-      </c>
-      <c r="P2" t="n">
-        <v>84872886.86</v>
-      </c>
+        <v>5015048365.73</v>
+      </c>
+      <c r="P2" t="inlineStr"/>
       <c r="Q2" t="n">
-        <v>109829289.62</v>
+        <v>150126558.82</v>
       </c>
       <c r="R2" t="n">
-        <v>2013276255.88</v>
+        <v>1677698354.58</v>
       </c>
       <c r="S2" t="n">
-        <v>1869304080.36</v>
+        <v>1945002470.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1250985791</v>
+        <v>1270529500</v>
       </c>
       <c r="U2" t="n">
-        <v>1250985791</v>
-      </c>
-      <c r="V2" t="inlineStr"/>
+        <v>1270529500</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0</v>
+      </c>
       <c r="W2" t="n">
-        <v>2503515228.51</v>
+        <v>842981285.08</v>
       </c>
       <c r="X2" t="n">
-        <v>1361079005.68</v>
+        <v>70641671.98</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>111717414.55</v>
+        <v>36348271.61</v>
       </c>
       <c r="AA2" t="n">
-        <v>1711008.87</v>
+        <v>681980.83</v>
       </c>
       <c r="AB2" t="n">
-        <v>1247650582.26</v>
+        <v>33611419.54</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3611419.54</v>
       </c>
       <c r="AD2" t="n">
-        <v>1247650582.26</v>
+        <v>30000000</v>
       </c>
       <c r="AE2" t="n">
-        <v>1142436222.83</v>
+        <v>772339613.1</v>
       </c>
       <c r="AF2" t="n">
-        <v>94368972.61</v>
+        <v>80892491.64</v>
       </c>
       <c r="AG2" t="n">
-        <v>213564198.25</v>
+        <v>195422642.81</v>
       </c>
       <c r="AH2" t="n">
-        <v>192725995.43</v>
+        <v>172034482.27</v>
       </c>
       <c r="AI2" t="n">
-        <v>821190465.0700001</v>
+        <v>486653592.4</v>
       </c>
       <c r="AJ2" t="n">
-        <v>89091874.23</v>
+        <v>59713917.38</v>
       </c>
       <c r="AK2" t="n">
         <v>0</v>
       </c>
       <c r="AL2" t="n">
-        <v>33721570.48</v>
+        <v>47645567.95</v>
       </c>
       <c r="AM2" t="n">
-        <v>698377020.36</v>
+        <v>379294107.07</v>
       </c>
       <c r="AN2" t="n">
-        <v>8068022622.9</v>
+        <v>5866961154.7</v>
       </c>
       <c r="AO2" t="n">
-        <v>3184703741.99</v>
+        <v>2171933523.35</v>
       </c>
       <c r="AP2" t="n">
-        <v>225334414.54</v>
+        <v>134558056.46</v>
       </c>
       <c r="AQ2" t="n">
-        <v>225475.96</v>
+        <v>2060903.96</v>
       </c>
       <c r="AR2" t="n">
-        <v>29868904.14</v>
+        <v>22583317.52</v>
       </c>
       <c r="AS2" t="n">
         <v>0</v>
@@ -1890,46 +1888,46 @@
         <v>0</v>
       </c>
       <c r="AU2" t="n">
-        <v>35916196.46</v>
+        <v>0</v>
       </c>
       <c r="AV2" t="n">
         <v>0</v>
       </c>
       <c r="AW2" t="n">
-        <v>283163351.74</v>
+        <v>230398422.32</v>
       </c>
       <c r="AX2" t="n">
-        <v>283163351.74</v>
+        <v>230398422.32</v>
       </c>
       <c r="AY2" t="n">
         <v>0</v>
       </c>
       <c r="AZ2" t="n">
-        <v>2610195399.15</v>
+        <v>1782332823.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>-1398483421.8</v>
+        <v>-1015029782.85</v>
       </c>
       <c r="BB2" t="n">
-        <v>4008678820.95</v>
+        <v>2797362605.94</v>
       </c>
       <c r="BC2" t="n">
-        <v>525138271.92</v>
+        <v>193551755.76</v>
       </c>
       <c r="BD2" t="n">
-        <v>95463231.03</v>
+        <v>76977874.09999999</v>
       </c>
       <c r="BE2" t="n">
-        <v>2037710467.3</v>
+        <v>1696817468.65</v>
       </c>
       <c r="BF2" t="n">
-        <v>1350366850.7</v>
+        <v>830015507.4299999</v>
       </c>
       <c r="BG2" t="n">
-        <v>4883318880.91</v>
+        <v>3695027631.35</v>
       </c>
       <c r="BH2" t="n">
-        <v>568685203.03</v>
+        <v>205820281.3</v>
       </c>
       <c r="BI2" t="n">
         <v>0</v>
@@ -1937,185 +1935,183 @@
       <c r="BJ2" t="n">
         <v>0</v>
       </c>
-      <c r="BK2" t="inlineStr"/>
+      <c r="BK2" t="n">
+        <v>0</v>
+      </c>
       <c r="BL2" t="n">
-        <v>32335642.61</v>
+        <v>77674772.16</v>
       </c>
       <c r="BM2" t="n">
-        <v>648692940.76</v>
+        <v>604341456.9299999</v>
       </c>
       <c r="BN2" t="n">
         <v>0</v>
       </c>
       <c r="BO2" t="n">
-        <v>279356283.67</v>
+        <v>227938607.73</v>
       </c>
       <c r="BP2" t="n">
-        <v>251551583.31</v>
+        <v>241613413.22</v>
       </c>
       <c r="BQ2" t="n">
-        <v>117785073.78</v>
+        <v>134789435.98</v>
       </c>
       <c r="BR2" t="n">
-        <v>370079092.99</v>
+        <v>556485625.65</v>
       </c>
       <c r="BS2" t="n">
-        <v>2163902215.74</v>
+        <v>1461298812.97</v>
       </c>
       <c r="BT2" t="n">
-        <v>-118286110.87</v>
+        <v>-78591793.36</v>
       </c>
       <c r="BU2" t="n">
-        <v>2282188326.61</v>
+        <v>1539890606.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>1099623785.78</v>
+        <v>789406682.34</v>
       </c>
       <c r="BW2" t="n">
-        <v>280683981.98</v>
+        <v>141873803.89</v>
       </c>
       <c r="BX2" t="n">
-        <v>818939803.8</v>
+        <v>647532878.45</v>
       </c>
       <c r="BY2" t="n">
-        <v>4064380.98</v>
+        <v>21253721.65</v>
       </c>
       <c r="BZ2" t="n">
-        <v>814875422.8200001</v>
+        <v>626279156.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>1250183651</v>
+        <v>1250169663</v>
       </c>
       <c r="C3" t="n">
-        <v>1250183651</v>
-      </c>
-      <c r="D3" t="n">
-        <v>280351876.32</v>
-      </c>
+        <v>1250169663</v>
+      </c>
+      <c r="D3" t="inlineStr"/>
       <c r="E3" t="n">
-        <v>1143525743.82</v>
+        <v>120152706.43</v>
       </c>
       <c r="F3" t="n">
-        <v>5362074793.23</v>
+        <v>5327947899.95</v>
       </c>
       <c r="G3" t="n">
-        <v>6788608791.21</v>
+        <v>5660725945.73</v>
       </c>
       <c r="H3" t="n">
-        <v>4287272731.32</v>
+        <v>3315020331.4</v>
       </c>
       <c r="I3" t="n">
-        <v>5362074793.23</v>
+        <v>5327947899.95</v>
       </c>
       <c r="J3" t="n">
-        <v>2256813.78</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>5652358933.83</v>
+        <v>5544184658.8</v>
       </c>
       <c r="L3" t="n">
-        <v>6751880529.83</v>
+        <v>5544184658.8</v>
       </c>
       <c r="M3" t="n">
-        <v>5676178608.05</v>
+        <v>5566367062.61</v>
       </c>
       <c r="N3" t="n">
-        <v>23819674.22</v>
+        <v>22182403.81</v>
       </c>
       <c r="O3" t="n">
-        <v>5652358933.83</v>
-      </c>
-      <c r="P3" t="n">
-        <v>84876534.11</v>
-      </c>
+        <v>5544184658.8</v>
+      </c>
+      <c r="P3" t="inlineStr"/>
       <c r="Q3" t="n">
-        <v>126335937.42</v>
+        <v>89120327.04000001</v>
       </c>
       <c r="R3" t="n">
-        <v>2203926912.12</v>
+        <v>2187216021.14</v>
       </c>
       <c r="S3" t="n">
-        <v>1850701682.37</v>
+        <v>1873876951.93</v>
       </c>
       <c r="T3" t="n">
-        <v>1250183651</v>
+        <v>1250169663</v>
       </c>
       <c r="U3" t="n">
-        <v>1250183651</v>
+        <v>1250169663</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
       <c r="W3" t="n">
-        <v>2031598614.44</v>
+        <v>816479272.79</v>
       </c>
       <c r="X3" t="n">
-        <v>1209239074.85</v>
+        <v>35490563.31</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>106911805.01</v>
+        <v>33293217.6</v>
       </c>
       <c r="AA3" t="n">
-        <v>548860.0600000001</v>
+        <v>2197345.71</v>
       </c>
       <c r="AB3" t="n">
-        <v>1101778409.78</v>
+        <v>0</v>
       </c>
       <c r="AC3" t="n">
-        <v>2256813.78</v>
+        <v>0</v>
       </c>
       <c r="AD3" t="n">
-        <v>1099521596</v>
+        <v>0</v>
       </c>
       <c r="AE3" t="n">
-        <v>822359539.59</v>
+        <v>780988709.48</v>
       </c>
       <c r="AF3" t="n">
-        <v>98820855.23</v>
+        <v>91132596.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>41747334.04</v>
+        <v>120152706.43</v>
       </c>
       <c r="AH3" t="n">
-        <v>36728261.38</v>
+        <v>116541286.93</v>
       </c>
       <c r="AI3" t="n">
-        <v>672625528.79</v>
+        <v>558936201.29</v>
       </c>
       <c r="AJ3" t="n">
-        <v>106131605.23</v>
+        <v>64370966.22</v>
       </c>
       <c r="AK3" t="n">
         <v>0</v>
       </c>
       <c r="AL3" t="n">
-        <v>62030766.82</v>
+        <v>68286834.38</v>
       </c>
       <c r="AM3" t="n">
-        <v>504463156.74</v>
+        <v>426278400.69</v>
       </c>
       <c r="AN3" t="n">
-        <v>7707777222.49</v>
+        <v>6382846335.4</v>
       </c>
       <c r="AO3" t="n">
-        <v>2598144951.58</v>
+        <v>2286837294.52</v>
       </c>
       <c r="AP3" t="n">
-        <v>113282173.69</v>
+        <v>51848959.89</v>
       </c>
       <c r="AQ3" t="n">
-        <v>9146217.42</v>
+        <v>969013.51</v>
       </c>
       <c r="AR3" t="n">
-        <v>25925333.16</v>
+        <v>26156399.24</v>
       </c>
       <c r="AS3" t="n">
         <v>0</v>
@@ -2124,46 +2120,46 @@
         <v>0</v>
       </c>
       <c r="AU3" t="n">
-        <v>32365903.1</v>
+        <v>13366074.99</v>
       </c>
       <c r="AV3" t="n">
         <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>290284140.6</v>
+        <v>216236758.85</v>
       </c>
       <c r="AX3" t="n">
-        <v>290284140.6</v>
+        <v>216236758.85</v>
       </c>
       <c r="AY3" t="n">
         <v>0</v>
       </c>
       <c r="AZ3" t="n">
-        <v>2127141183.61</v>
+        <v>1978260088.04</v>
       </c>
       <c r="BA3" t="n">
-        <v>-1265740094.64</v>
+        <v>-1062501532.61</v>
       </c>
       <c r="BB3" t="n">
-        <v>3392881278.25</v>
+        <v>3040761620.65</v>
       </c>
       <c r="BC3" t="n">
-        <v>442123787.52</v>
+        <v>317707377.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>80523367.08</v>
+        <v>68871974.92</v>
       </c>
       <c r="BE3" t="n">
-        <v>2057312076.9</v>
+        <v>1861003635.37</v>
       </c>
       <c r="BF3" t="n">
-        <v>812922046.75</v>
+        <v>793178632.5599999</v>
       </c>
       <c r="BG3" t="n">
-        <v>5109632270.91</v>
+        <v>4096009040.88</v>
       </c>
       <c r="BH3" t="n">
-        <v>618455678.61</v>
+        <v>131324988.9</v>
       </c>
       <c r="BI3" t="n">
         <v>0</v>
@@ -2175,179 +2171,183 @@
         <v>0</v>
       </c>
       <c r="BL3" t="n">
-        <v>45686775.23</v>
+        <v>59954107.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>635723055.83</v>
+        <v>670797068.83</v>
       </c>
       <c r="BN3" t="n">
         <v>0</v>
       </c>
       <c r="BO3" t="n">
-        <v>279315195.53</v>
+        <v>287001437.29</v>
       </c>
       <c r="BP3" t="n">
-        <v>253910755.08</v>
+        <v>251353566.08</v>
       </c>
       <c r="BQ3" t="n">
-        <v>102497105.22</v>
+        <v>132442065.46</v>
       </c>
       <c r="BR3" t="n">
-        <v>477690073.33</v>
+        <v>529299236.25</v>
       </c>
       <c r="BS3" t="n">
-        <v>2120919285.28</v>
+        <v>1707122340.57</v>
       </c>
       <c r="BT3" t="n">
-        <v>-115395142.26</v>
+        <v>-93003323.2</v>
       </c>
       <c r="BU3" t="n">
-        <v>2236314427.54</v>
+        <v>1800125663.77</v>
       </c>
       <c r="BV3" t="n">
-        <v>1211157402.63</v>
+        <v>997511298.45</v>
       </c>
       <c r="BW3" t="n">
-        <v>355259421.57</v>
+        <v>138306897.07</v>
       </c>
       <c r="BX3" t="n">
-        <v>855897981.0599999</v>
+        <v>859204401.38</v>
       </c>
       <c r="BY3" t="n">
-        <v>5373842.8</v>
+        <v>22312146.35</v>
       </c>
       <c r="BZ3" t="n">
-        <v>850524138.26</v>
+        <v>836892255.03</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1250169663</v>
+        <v>1250183651</v>
       </c>
       <c r="C4" t="n">
-        <v>1250169663</v>
-      </c>
-      <c r="D4" t="inlineStr"/>
+        <v>1250183651</v>
+      </c>
+      <c r="D4" t="n">
+        <v>280351876.32</v>
+      </c>
       <c r="E4" t="n">
-        <v>120152706.43</v>
+        <v>1143525743.82</v>
       </c>
       <c r="F4" t="n">
-        <v>5327947899.95</v>
+        <v>5362074793.23</v>
       </c>
       <c r="G4" t="n">
-        <v>5660725945.73</v>
+        <v>6788608791.21</v>
       </c>
       <c r="H4" t="n">
-        <v>3315020331.4</v>
+        <v>4287272731.32</v>
       </c>
       <c r="I4" t="n">
-        <v>5327947899.95</v>
+        <v>5362074793.23</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>2256813.78</v>
       </c>
       <c r="K4" t="n">
-        <v>5544184658.8</v>
+        <v>5652358933.83</v>
       </c>
       <c r="L4" t="n">
-        <v>5544184658.8</v>
+        <v>6751880529.83</v>
       </c>
       <c r="M4" t="n">
-        <v>5566367062.61</v>
+        <v>5676178608.05</v>
       </c>
       <c r="N4" t="n">
-        <v>22182403.81</v>
+        <v>23819674.22</v>
       </c>
       <c r="O4" t="n">
-        <v>5544184658.8</v>
-      </c>
-      <c r="P4" t="inlineStr"/>
+        <v>5652358933.83</v>
+      </c>
+      <c r="P4" t="n">
+        <v>84876534.11</v>
+      </c>
       <c r="Q4" t="n">
-        <v>89120327.04000001</v>
+        <v>126335937.42</v>
       </c>
       <c r="R4" t="n">
-        <v>2187216021.14</v>
+        <v>2203926912.12</v>
       </c>
       <c r="S4" t="n">
-        <v>1873876951.93</v>
+        <v>1850701682.37</v>
       </c>
       <c r="T4" t="n">
-        <v>1250169663</v>
+        <v>1250183651</v>
       </c>
       <c r="U4" t="n">
-        <v>1250169663</v>
+        <v>1250183651</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>816479272.79</v>
+        <v>2031598614.44</v>
       </c>
       <c r="X4" t="n">
-        <v>35490563.31</v>
+        <v>1209239074.85</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>33293217.6</v>
+        <v>106911805.01</v>
       </c>
       <c r="AA4" t="n">
-        <v>2197345.71</v>
+        <v>548860.0600000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1101778409.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>2256813.78</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1099521596</v>
       </c>
       <c r="AE4" t="n">
-        <v>780988709.48</v>
+        <v>822359539.59</v>
       </c>
       <c r="AF4" t="n">
-        <v>91132596.25</v>
+        <v>98820855.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>120152706.43</v>
+        <v>41747334.04</v>
       </c>
       <c r="AH4" t="n">
-        <v>116541286.93</v>
+        <v>36728261.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>558936201.29</v>
+        <v>672625528.79</v>
       </c>
       <c r="AJ4" t="n">
-        <v>64370966.22</v>
+        <v>106131605.23</v>
       </c>
       <c r="AK4" t="n">
         <v>0</v>
       </c>
       <c r="AL4" t="n">
-        <v>68286834.38</v>
+        <v>62030766.82</v>
       </c>
       <c r="AM4" t="n">
-        <v>426278400.69</v>
+        <v>504463156.74</v>
       </c>
       <c r="AN4" t="n">
-        <v>6382846335.4</v>
+        <v>7707777222.49</v>
       </c>
       <c r="AO4" t="n">
-        <v>2286837294.52</v>
+        <v>2598144951.58</v>
       </c>
       <c r="AP4" t="n">
-        <v>51848959.89</v>
+        <v>113282173.69</v>
       </c>
       <c r="AQ4" t="n">
-        <v>969013.51</v>
+        <v>9146217.42</v>
       </c>
       <c r="AR4" t="n">
-        <v>26156399.24</v>
+        <v>25925333.16</v>
       </c>
       <c r="AS4" t="n">
         <v>0</v>
@@ -2356,46 +2356,46 @@
         <v>0</v>
       </c>
       <c r="AU4" t="n">
-        <v>13366074.99</v>
+        <v>32365903.1</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
       </c>
       <c r="AW4" t="n">
-        <v>216236758.85</v>
+        <v>290284140.6</v>
       </c>
       <c r="AX4" t="n">
-        <v>216236758.85</v>
+        <v>290284140.6</v>
       </c>
       <c r="AY4" t="n">
         <v>0</v>
       </c>
       <c r="AZ4" t="n">
-        <v>1978260088.04</v>
+        <v>2127141183.61</v>
       </c>
       <c r="BA4" t="n">
-        <v>-1062501532.61</v>
+        <v>-1265740094.64</v>
       </c>
       <c r="BB4" t="n">
-        <v>3040761620.65</v>
+        <v>3392881278.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>317707377.8</v>
+        <v>442123787.52</v>
       </c>
       <c r="BD4" t="n">
-        <v>68871974.92</v>
+        <v>80523367.08</v>
       </c>
       <c r="BE4" t="n">
-        <v>1861003635.37</v>
+        <v>2057312076.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>793178632.5599999</v>
+        <v>812922046.75</v>
       </c>
       <c r="BG4" t="n">
-        <v>4096009040.88</v>
+        <v>5109632270.91</v>
       </c>
       <c r="BH4" t="n">
-        <v>131324988.9</v>
+        <v>618455678.61</v>
       </c>
       <c r="BI4" t="n">
         <v>0</v>
@@ -2407,179 +2407,181 @@
         <v>0</v>
       </c>
       <c r="BL4" t="n">
-        <v>59954107.88</v>
+        <v>45686775.23</v>
       </c>
       <c r="BM4" t="n">
-        <v>670797068.83</v>
+        <v>635723055.83</v>
       </c>
       <c r="BN4" t="n">
         <v>0</v>
       </c>
       <c r="BO4" t="n">
-        <v>287001437.29</v>
+        <v>279315195.53</v>
       </c>
       <c r="BP4" t="n">
-        <v>251353566.08</v>
+        <v>253910755.08</v>
       </c>
       <c r="BQ4" t="n">
-        <v>132442065.46</v>
+        <v>102497105.22</v>
       </c>
       <c r="BR4" t="n">
-        <v>529299236.25</v>
+        <v>477690073.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>1707122340.57</v>
+        <v>2120919285.28</v>
       </c>
       <c r="BT4" t="n">
-        <v>-93003323.2</v>
+        <v>-115395142.26</v>
       </c>
       <c r="BU4" t="n">
-        <v>1800125663.77</v>
+        <v>2236314427.54</v>
       </c>
       <c r="BV4" t="n">
-        <v>997511298.45</v>
+        <v>1211157402.63</v>
       </c>
       <c r="BW4" t="n">
-        <v>138306897.07</v>
+        <v>355259421.57</v>
       </c>
       <c r="BX4" t="n">
-        <v>859204401.38</v>
+        <v>855897981.0599999</v>
       </c>
       <c r="BY4" t="n">
-        <v>22312146.35</v>
+        <v>5373842.8</v>
       </c>
       <c r="BZ4" t="n">
-        <v>836892255.03</v>
+        <v>850524138.26</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>1270529500</v>
+        <v>1251285791</v>
       </c>
       <c r="C5" t="n">
-        <v>1270529500</v>
-      </c>
-      <c r="D5" t="inlineStr"/>
+        <v>1251285791</v>
+      </c>
+      <c r="D5" t="n">
+        <v>621436773.89</v>
+      </c>
       <c r="E5" t="n">
-        <v>229034062.35</v>
+        <v>1461214780.51</v>
       </c>
       <c r="F5" t="n">
-        <v>4784649943.41</v>
+        <v>5276507911.52</v>
       </c>
       <c r="G5" t="n">
-        <v>5217082848</v>
+        <v>7000047840.95</v>
       </c>
       <c r="H5" t="n">
-        <v>2922688018.25</v>
+        <v>3740882658.08</v>
       </c>
       <c r="I5" t="n">
-        <v>4784649943.41</v>
+        <v>5276507911.52</v>
       </c>
       <c r="J5" t="n">
-        <v>3611419.54</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>5015048365.73</v>
+        <v>5559671263.26</v>
       </c>
       <c r="L5" t="n">
-        <v>5045048365.73</v>
+        <v>6807321845.52</v>
       </c>
       <c r="M5" t="n">
-        <v>5023979869.62</v>
+        <v>5564507394.39</v>
       </c>
       <c r="N5" t="n">
-        <v>8931503.890000001</v>
+        <v>4836131.13</v>
       </c>
       <c r="O5" t="n">
-        <v>5015048365.73</v>
-      </c>
-      <c r="P5" t="inlineStr"/>
+        <v>5559671263.26</v>
+      </c>
+      <c r="P5" t="n">
+        <v>84872886.86</v>
+      </c>
       <c r="Q5" t="n">
-        <v>150126558.82</v>
+        <v>109829289.62</v>
       </c>
       <c r="R5" t="n">
-        <v>1677698354.58</v>
+        <v>2013276255.88</v>
       </c>
       <c r="S5" t="n">
-        <v>1945002470.2</v>
+        <v>1869304080.36</v>
       </c>
       <c r="T5" t="n">
-        <v>1270529500</v>
+        <v>1250985791</v>
       </c>
       <c r="U5" t="n">
-        <v>1270529500</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0</v>
-      </c>
+        <v>1250985791</v>
+      </c>
+      <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>842981285.08</v>
+        <v>2503515228.51</v>
       </c>
       <c r="X5" t="n">
-        <v>70641671.98</v>
+        <v>1361079005.68</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>36348271.61</v>
+        <v>111717414.55</v>
       </c>
       <c r="AA5" t="n">
-        <v>681980.83</v>
+        <v>1711008.87</v>
       </c>
       <c r="AB5" t="n">
-        <v>33611419.54</v>
+        <v>1247650582.26</v>
       </c>
       <c r="AC5" t="n">
-        <v>3611419.54</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>30000000</v>
+        <v>1247650582.26</v>
       </c>
       <c r="AE5" t="n">
-        <v>772339613.1</v>
+        <v>1142436222.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>80892491.64</v>
+        <v>94368972.61</v>
       </c>
       <c r="AG5" t="n">
-        <v>195422642.81</v>
+        <v>213564198.25</v>
       </c>
       <c r="AH5" t="n">
-        <v>172034482.27</v>
+        <v>192725995.43</v>
       </c>
       <c r="AI5" t="n">
-        <v>486653592.4</v>
+        <v>821190465.0700001</v>
       </c>
       <c r="AJ5" t="n">
-        <v>59713917.38</v>
+        <v>89091874.23</v>
       </c>
       <c r="AK5" t="n">
         <v>0</v>
       </c>
       <c r="AL5" t="n">
-        <v>47645567.95</v>
+        <v>33721570.48</v>
       </c>
       <c r="AM5" t="n">
-        <v>379294107.07</v>
+        <v>698377020.36</v>
       </c>
       <c r="AN5" t="n">
-        <v>5866961154.7</v>
+        <v>8068022622.9</v>
       </c>
       <c r="AO5" t="n">
-        <v>2171933523.35</v>
+        <v>3184703741.99</v>
       </c>
       <c r="AP5" t="n">
-        <v>134558056.46</v>
+        <v>225334414.54</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2060903.96</v>
+        <v>225475.96</v>
       </c>
       <c r="AR5" t="n">
-        <v>22583317.52</v>
+        <v>29868904.14</v>
       </c>
       <c r="AS5" t="n">
         <v>0</v>
@@ -2588,46 +2590,46 @@
         <v>0</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>35916196.46</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
       </c>
       <c r="AW5" t="n">
-        <v>230398422.32</v>
+        <v>283163351.74</v>
       </c>
       <c r="AX5" t="n">
-        <v>230398422.32</v>
+        <v>283163351.74</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
       </c>
       <c r="AZ5" t="n">
-        <v>1782332823.09</v>
+        <v>2610195399.15</v>
       </c>
       <c r="BA5" t="n">
-        <v>-1015029782.85</v>
+        <v>-1398483421.8</v>
       </c>
       <c r="BB5" t="n">
-        <v>2797362605.94</v>
+        <v>4008678820.95</v>
       </c>
       <c r="BC5" t="n">
-        <v>193551755.76</v>
+        <v>525138271.92</v>
       </c>
       <c r="BD5" t="n">
-        <v>76977874.09999999</v>
+        <v>95463231.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>1696817468.65</v>
+        <v>2037710467.3</v>
       </c>
       <c r="BF5" t="n">
-        <v>830015507.4299999</v>
+        <v>1350366850.7</v>
       </c>
       <c r="BG5" t="n">
-        <v>3695027631.35</v>
+        <v>4883318880.91</v>
       </c>
       <c r="BH5" t="n">
-        <v>205820281.3</v>
+        <v>568685203.03</v>
       </c>
       <c r="BI5" t="n">
         <v>0</v>
@@ -2635,53 +2637,51 @@
       <c r="BJ5" t="n">
         <v>0</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0</v>
-      </c>
+      <c r="BK5" t="inlineStr"/>
       <c r="BL5" t="n">
-        <v>77674772.16</v>
+        <v>32335642.61</v>
       </c>
       <c r="BM5" t="n">
-        <v>604341456.9299999</v>
+        <v>648692940.76</v>
       </c>
       <c r="BN5" t="n">
         <v>0</v>
       </c>
       <c r="BO5" t="n">
-        <v>227938607.73</v>
+        <v>279356283.67</v>
       </c>
       <c r="BP5" t="n">
-        <v>241613413.22</v>
+        <v>251551583.31</v>
       </c>
       <c r="BQ5" t="n">
-        <v>134789435.98</v>
+        <v>117785073.78</v>
       </c>
       <c r="BR5" t="n">
-        <v>556485625.65</v>
+        <v>370079092.99</v>
       </c>
       <c r="BS5" t="n">
-        <v>1461298812.97</v>
+        <v>2163902215.74</v>
       </c>
       <c r="BT5" t="n">
-        <v>-78591793.36</v>
+        <v>-118286110.87</v>
       </c>
       <c r="BU5" t="n">
-        <v>1539890606.33</v>
+        <v>2282188326.61</v>
       </c>
       <c r="BV5" t="n">
-        <v>789406682.34</v>
+        <v>1099623785.78</v>
       </c>
       <c r="BW5" t="n">
-        <v>141873803.89</v>
+        <v>280683981.98</v>
       </c>
       <c r="BX5" t="n">
-        <v>647532878.45</v>
+        <v>818939803.8</v>
       </c>
       <c r="BY5" t="n">
-        <v>21253721.65</v>
+        <v>4064380.98</v>
       </c>
       <c r="BZ5" t="n">
-        <v>626279156.8</v>
+        <v>814875422.8200001</v>
       </c>
     </row>
   </sheetData>
@@ -2952,128 +2952,130 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>120552183.85</v>
+        <v>-436616213.18</v>
       </c>
       <c r="C2" t="n">
-        <v>-102000000</v>
+        <v>-202161082</v>
       </c>
       <c r="D2" t="n">
-        <v>401206008.3</v>
+        <v>264249559.78</v>
       </c>
       <c r="E2" t="n">
-        <v>-208353942.5</v>
+        <v>-123548852.69</v>
       </c>
       <c r="F2" t="n">
-        <v>814730963.1</v>
+        <v>626291236.42</v>
       </c>
       <c r="G2" t="n">
-        <v>851259086.73</v>
+        <v>498169217.64</v>
       </c>
       <c r="H2" t="n">
-        <v>5707912.98</v>
+        <v>-2626064.13</v>
       </c>
       <c r="I2" t="n">
-        <v>-42236036.61</v>
+        <v>130748082.91</v>
       </c>
       <c r="J2" t="n">
-        <v>-299463614.8</v>
+        <v>29529291.17</v>
       </c>
       <c r="K2" t="n">
-        <v>2612437.07</v>
+        <v>43871883.72</v>
       </c>
       <c r="L2" t="n">
-        <v>-601282060.17</v>
+        <v>-76431070.33</v>
       </c>
       <c r="M2" t="n">
-        <v>299206008.3</v>
+        <v>62088477.78</v>
       </c>
       <c r="N2" t="n">
-        <v>299206008.3</v>
+        <v>62088477.78</v>
       </c>
       <c r="O2" t="n">
-        <v>-102000000</v>
+        <v>-202161082</v>
       </c>
       <c r="P2" t="n">
-        <v>401206008.3</v>
+        <v>264249559.78</v>
       </c>
       <c r="Q2" t="n">
-        <v>-71678548.16</v>
-      </c>
-      <c r="R2" t="inlineStr"/>
+        <v>414286152.23</v>
+      </c>
+      <c r="R2" t="n">
+        <v>8022056.71</v>
+      </c>
       <c r="S2" t="n">
-        <v>123990443.24</v>
+        <v>520760453.85</v>
       </c>
       <c r="T2" t="n">
-        <v>2390886944.74</v>
+        <v>5319857210.14</v>
       </c>
       <c r="U2" t="n">
-        <v>-2266896501.5</v>
+        <v>-4799096756.29</v>
       </c>
       <c r="V2" t="n">
-        <v>9226246.49</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>9226246.49</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>-204895237.89</v>
+        <v>-114496358.33</v>
       </c>
       <c r="Z2" t="n">
-        <v>3458704.61</v>
+        <v>9052494.359999999</v>
       </c>
       <c r="AA2" t="n">
-        <v>-208353942.5</v>
+        <v>-123548852.69</v>
       </c>
       <c r="AB2" t="n">
-        <v>328906126.35</v>
+        <v>-313067360.49</v>
       </c>
       <c r="AC2" t="n">
-        <v>-428858577.88</v>
+        <v>-886422924.9</v>
       </c>
       <c r="AD2" t="n">
-        <v>-2606569.13</v>
+        <v>-6162061.88</v>
       </c>
       <c r="AE2" t="n">
-        <v>57209286.76</v>
+        <v>128587216.57</v>
       </c>
       <c r="AF2" t="n">
-        <v>-19995651.23</v>
+        <v>-155284395.81</v>
       </c>
       <c r="AG2" t="n">
-        <v>-463465644.28</v>
+        <v>-853563683.78</v>
       </c>
       <c r="AH2" t="n">
-        <v>42794265.47</v>
+        <v>5266671.52</v>
       </c>
       <c r="AI2" t="n">
-        <v>227906764.32</v>
+        <v>183605452.41</v>
       </c>
       <c r="AJ2" t="n">
-        <v>7305362.31</v>
+        <v>5962211.54</v>
       </c>
       <c r="AK2" t="n">
-        <v>220601402.01</v>
+        <v>177643240.87</v>
       </c>
       <c r="AL2" t="n">
-        <v>-16109052.15</v>
+        <v>-17757842.34</v>
       </c>
       <c r="AM2" t="n">
-        <v>5846461.49</v>
+        <v>-92310612.03</v>
       </c>
       <c r="AN2" t="n">
-        <v>462768262.53</v>
+        <v>458082156.64</v>
       </c>
       <c r="AO2" t="n">
-        <v>328906126.35</v>
+        <v>-313067360.49</v>
       </c>
       <c r="AP2" t="n">
-        <v>-148637197.04</v>
+        <v>-94969188.91</v>
       </c>
       <c r="AQ2" t="n">
         <v>0</v>
@@ -3082,88 +3084,88 @@
         <v>0</v>
       </c>
       <c r="AS2" t="n">
-        <v>-6703684327.47</v>
+        <v>-5724136695.81</v>
       </c>
       <c r="AT2" t="n">
-        <v>-283302723.48</v>
+        <v>-173713008.1</v>
       </c>
       <c r="AU2" t="n">
-        <v>-532575439.75</v>
+        <v>-421464611.82</v>
       </c>
       <c r="AV2" t="n">
-        <v>-5887806164.24</v>
+        <v>-5128959075.89</v>
       </c>
       <c r="AW2" t="n">
-        <v>7181227650.86</v>
+        <v>5506038524.23</v>
       </c>
       <c r="AX2" t="n">
-        <v>98061171.7</v>
+        <v>35594088.28</v>
       </c>
       <c r="AY2" t="n">
-        <v>7083166479.16</v>
+        <v>5470444435.95</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>190481820.87</v>
+        <v>-71039918.34</v>
       </c>
       <c r="C3" t="n">
-        <v>-173342948.27</v>
+        <v>-308026030</v>
       </c>
       <c r="D3" t="n">
-        <v>99900000</v>
+        <v>131692931.69</v>
       </c>
       <c r="E3" t="n">
-        <v>-189012668.91</v>
+        <v>-98063002.90000001</v>
       </c>
       <c r="F3" t="n">
-        <v>851259086.73</v>
+        <v>849562293.96</v>
       </c>
       <c r="G3" t="n">
-        <v>849562293.96</v>
+        <v>626291236.42</v>
       </c>
       <c r="H3" t="n">
-        <v>7623033.12</v>
+        <v>14046164.61</v>
       </c>
       <c r="I3" t="n">
-        <v>-5926240.35</v>
+        <v>209224892.93</v>
       </c>
       <c r="J3" t="n">
-        <v>562949783.28</v>
+        <v>-236249879.78</v>
       </c>
       <c r="K3" t="n">
-        <v>1140255435.46</v>
+        <v>67121484.77</v>
       </c>
       <c r="L3" t="n">
-        <v>-503862703.91</v>
+        <v>-127038266.24</v>
       </c>
       <c r="M3" t="n">
-        <v>-73442948.27</v>
+        <v>-176333098.31</v>
       </c>
       <c r="N3" t="n">
-        <v>-73442948.27</v>
+        <v>-176333098.31</v>
       </c>
       <c r="O3" t="n">
-        <v>-173342948.27</v>
+        <v>-308026030</v>
       </c>
       <c r="P3" t="n">
-        <v>99900000</v>
+        <v>131692931.69</v>
       </c>
       <c r="Q3" t="n">
-        <v>-948370513.41</v>
+        <v>418451688.15</v>
       </c>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="n">
-        <v>-760927180.2</v>
+        <v>98193580.75</v>
       </c>
       <c r="T3" t="n">
-        <v>890207754.37</v>
+        <v>4572628490.63</v>
       </c>
       <c r="U3" t="n">
-        <v>-1651134934.57</v>
+        <v>-4474434909.88</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -3175,58 +3177,58 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>-187443333.21</v>
+        <v>320258107.4</v>
       </c>
       <c r="Z3" t="n">
-        <v>1569335.7</v>
+        <v>418321110.3</v>
       </c>
       <c r="AA3" t="n">
-        <v>-189012668.91</v>
+        <v>-98063002.90000001</v>
       </c>
       <c r="AB3" t="n">
-        <v>379494489.78</v>
+        <v>27023084.56</v>
       </c>
       <c r="AC3" t="n">
-        <v>-526671957.66</v>
+        <v>-570554249.98</v>
       </c>
       <c r="AD3" t="n">
-        <v>-16539017.26</v>
+        <v>-1989958.21</v>
       </c>
       <c r="AE3" t="n">
-        <v>159460280.94</v>
+        <v>116359802.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>33223573.27</v>
+        <v>-71039954.06</v>
       </c>
       <c r="AG3" t="n">
-        <v>-702816794.61</v>
+        <v>-613884139.98</v>
       </c>
       <c r="AH3" t="n">
-        <v>31651951.31</v>
+        <v>-8924098.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>225198587.42</v>
+        <v>204432762.07</v>
       </c>
       <c r="AJ3" t="n">
-        <v>6898913.29</v>
+        <v>5893707.17</v>
       </c>
       <c r="AK3" t="n">
-        <v>218299674.13</v>
+        <v>198539054.9</v>
       </c>
       <c r="AL3" t="n">
-        <v>-22719906.59</v>
+        <v>-1011650.77</v>
       </c>
       <c r="AM3" t="n">
-        <v>1937994.48</v>
+        <v>-289174686.91</v>
       </c>
       <c r="AN3" t="n">
-        <v>561841658.3099999</v>
+        <v>674830010.25</v>
       </c>
       <c r="AO3" t="n">
-        <v>379494489.78</v>
+        <v>27023084.56</v>
       </c>
       <c r="AP3" t="n">
-        <v>-159010473.45</v>
+        <v>-124662646</v>
       </c>
       <c r="AQ3" t="n">
         <v>0</v>
@@ -3235,88 +3237,88 @@
         <v>0</v>
       </c>
       <c r="AS3" t="n">
-        <v>-6100174378.16</v>
+        <v>-6166206404.24</v>
       </c>
       <c r="AT3" t="n">
-        <v>-226965020.6</v>
+        <v>-186700186.06</v>
       </c>
       <c r="AU3" t="n">
-        <v>-480151196.3</v>
+        <v>-463257349.54</v>
       </c>
       <c r="AV3" t="n">
-        <v>-5393058161.26</v>
+        <v>-5516248868.64</v>
       </c>
       <c r="AW3" t="n">
-        <v>6638679341.39</v>
+        <v>6317892134.8</v>
       </c>
       <c r="AX3" t="n">
-        <v>121005219.69</v>
+        <v>25642038.09</v>
       </c>
       <c r="AY3" t="n">
-        <v>6517674121.7</v>
+        <v>6292250096.71</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-71039918.34</v>
+        <v>190481820.87</v>
       </c>
       <c r="C4" t="n">
-        <v>-308026030</v>
+        <v>-173342948.27</v>
       </c>
       <c r="D4" t="n">
-        <v>131692931.69</v>
+        <v>99900000</v>
       </c>
       <c r="E4" t="n">
-        <v>-98063002.90000001</v>
+        <v>-189012668.91</v>
       </c>
       <c r="F4" t="n">
+        <v>851259086.73</v>
+      </c>
+      <c r="G4" t="n">
         <v>849562293.96</v>
       </c>
-      <c r="G4" t="n">
-        <v>626291236.42</v>
-      </c>
       <c r="H4" t="n">
-        <v>14046164.61</v>
+        <v>7623033.12</v>
       </c>
       <c r="I4" t="n">
-        <v>209224892.93</v>
+        <v>-5926240.35</v>
       </c>
       <c r="J4" t="n">
-        <v>-236249879.78</v>
+        <v>562949783.28</v>
       </c>
       <c r="K4" t="n">
-        <v>67121484.77</v>
+        <v>1140255435.46</v>
       </c>
       <c r="L4" t="n">
-        <v>-127038266.24</v>
+        <v>-503862703.91</v>
       </c>
       <c r="M4" t="n">
-        <v>-176333098.31</v>
+        <v>-73442948.27</v>
       </c>
       <c r="N4" t="n">
-        <v>-176333098.31</v>
+        <v>-73442948.27</v>
       </c>
       <c r="O4" t="n">
-        <v>-308026030</v>
+        <v>-173342948.27</v>
       </c>
       <c r="P4" t="n">
-        <v>131692931.69</v>
+        <v>99900000</v>
       </c>
       <c r="Q4" t="n">
-        <v>418451688.15</v>
+        <v>-948370513.41</v>
       </c>
       <c r="R4" t="inlineStr"/>
       <c r="S4" t="n">
-        <v>98193580.75</v>
+        <v>-760927180.2</v>
       </c>
       <c r="T4" t="n">
-        <v>4572628490.63</v>
+        <v>890207754.37</v>
       </c>
       <c r="U4" t="n">
-        <v>-4474434909.88</v>
+        <v>-1651134934.57</v>
       </c>
       <c r="V4" t="n">
         <v>0</v>
@@ -3328,58 +3330,58 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>320258107.4</v>
+        <v>-187443333.21</v>
       </c>
       <c r="Z4" t="n">
-        <v>418321110.3</v>
+        <v>1569335.7</v>
       </c>
       <c r="AA4" t="n">
-        <v>-98063002.90000001</v>
+        <v>-189012668.91</v>
       </c>
       <c r="AB4" t="n">
-        <v>27023084.56</v>
+        <v>379494489.78</v>
       </c>
       <c r="AC4" t="n">
-        <v>-570554249.98</v>
+        <v>-526671957.66</v>
       </c>
       <c r="AD4" t="n">
-        <v>-1989958.21</v>
+        <v>-16539017.26</v>
       </c>
       <c r="AE4" t="n">
-        <v>116359802.27</v>
+        <v>159460280.94</v>
       </c>
       <c r="AF4" t="n">
-        <v>-71039954.06</v>
+        <v>33223573.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>-613884139.98</v>
+        <v>-702816794.61</v>
       </c>
       <c r="AH4" t="n">
-        <v>-8924098.08</v>
+        <v>31651951.31</v>
       </c>
       <c r="AI4" t="n">
-        <v>204432762.07</v>
+        <v>225198587.42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>5893707.17</v>
+        <v>6898913.29</v>
       </c>
       <c r="AK4" t="n">
-        <v>198539054.9</v>
+        <v>218299674.13</v>
       </c>
       <c r="AL4" t="n">
-        <v>-1011650.77</v>
+        <v>-22719906.59</v>
       </c>
       <c r="AM4" t="n">
-        <v>-289174686.91</v>
+        <v>1937994.48</v>
       </c>
       <c r="AN4" t="n">
-        <v>674830010.25</v>
+        <v>561841658.3099999</v>
       </c>
       <c r="AO4" t="n">
-        <v>27023084.56</v>
+        <v>379494489.78</v>
       </c>
       <c r="AP4" t="n">
-        <v>-124662646</v>
+        <v>-159010473.45</v>
       </c>
       <c r="AQ4" t="n">
         <v>0</v>
@@ -3388,153 +3390,151 @@
         <v>0</v>
       </c>
       <c r="AS4" t="n">
-        <v>-6166206404.24</v>
+        <v>-6100174378.16</v>
       </c>
       <c r="AT4" t="n">
-        <v>-186700186.06</v>
+        <v>-226965020.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>-463257349.54</v>
+        <v>-480151196.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>-5516248868.64</v>
+        <v>-5393058161.26</v>
       </c>
       <c r="AW4" t="n">
-        <v>6317892134.8</v>
+        <v>6638679341.39</v>
       </c>
       <c r="AX4" t="n">
-        <v>25642038.09</v>
+        <v>121005219.69</v>
       </c>
       <c r="AY4" t="n">
-        <v>6292250096.71</v>
+        <v>6517674121.7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-436616213.18</v>
+        <v>120552183.85</v>
       </c>
       <c r="C5" t="n">
-        <v>-202161082</v>
+        <v>-102000000</v>
       </c>
       <c r="D5" t="n">
-        <v>264249559.78</v>
+        <v>401206008.3</v>
       </c>
       <c r="E5" t="n">
-        <v>-123548852.69</v>
+        <v>-208353942.5</v>
       </c>
       <c r="F5" t="n">
-        <v>626291236.42</v>
+        <v>814730963.1</v>
       </c>
       <c r="G5" t="n">
-        <v>498169217.64</v>
+        <v>851259086.73</v>
       </c>
       <c r="H5" t="n">
-        <v>-2626064.13</v>
+        <v>5707912.98</v>
       </c>
       <c r="I5" t="n">
-        <v>130748082.91</v>
+        <v>-42236036.61</v>
       </c>
       <c r="J5" t="n">
-        <v>29529291.17</v>
+        <v>-299463614.8</v>
       </c>
       <c r="K5" t="n">
-        <v>43871883.72</v>
+        <v>2612437.07</v>
       </c>
       <c r="L5" t="n">
-        <v>-76431070.33</v>
+        <v>-601282060.17</v>
       </c>
       <c r="M5" t="n">
-        <v>62088477.78</v>
+        <v>299206008.3</v>
       </c>
       <c r="N5" t="n">
-        <v>62088477.78</v>
+        <v>299206008.3</v>
       </c>
       <c r="O5" t="n">
-        <v>-202161082</v>
+        <v>-102000000</v>
       </c>
       <c r="P5" t="n">
-        <v>264249559.78</v>
+        <v>401206008.3</v>
       </c>
       <c r="Q5" t="n">
-        <v>414286152.23</v>
-      </c>
-      <c r="R5" t="n">
-        <v>8022056.71</v>
-      </c>
+        <v>-71678548.16</v>
+      </c>
+      <c r="R5" t="inlineStr"/>
       <c r="S5" t="n">
-        <v>520760453.85</v>
+        <v>123990443.24</v>
       </c>
       <c r="T5" t="n">
-        <v>5319857210.14</v>
+        <v>2390886944.74</v>
       </c>
       <c r="U5" t="n">
-        <v>-4799096756.29</v>
+        <v>-2266896501.5</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>9226246.49</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>9226246.49</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>-114496358.33</v>
+        <v>-204895237.89</v>
       </c>
       <c r="Z5" t="n">
-        <v>9052494.359999999</v>
+        <v>3458704.61</v>
       </c>
       <c r="AA5" t="n">
-        <v>-123548852.69</v>
+        <v>-208353942.5</v>
       </c>
       <c r="AB5" t="n">
-        <v>-313067360.49</v>
+        <v>328906126.35</v>
       </c>
       <c r="AC5" t="n">
-        <v>-886422924.9</v>
+        <v>-428858577.88</v>
       </c>
       <c r="AD5" t="n">
-        <v>-6162061.88</v>
+        <v>-2606569.13</v>
       </c>
       <c r="AE5" t="n">
-        <v>128587216.57</v>
+        <v>57209286.76</v>
       </c>
       <c r="AF5" t="n">
-        <v>-155284395.81</v>
+        <v>-19995651.23</v>
       </c>
       <c r="AG5" t="n">
-        <v>-853563683.78</v>
+        <v>-463465644.28</v>
       </c>
       <c r="AH5" t="n">
-        <v>5266671.52</v>
+        <v>42794265.47</v>
       </c>
       <c r="AI5" t="n">
-        <v>183605452.41</v>
+        <v>227906764.32</v>
       </c>
       <c r="AJ5" t="n">
-        <v>5962211.54</v>
+        <v>7305362.31</v>
       </c>
       <c r="AK5" t="n">
-        <v>177643240.87</v>
+        <v>220601402.01</v>
       </c>
       <c r="AL5" t="n">
-        <v>-17757842.34</v>
+        <v>-16109052.15</v>
       </c>
       <c r="AM5" t="n">
-        <v>-92310612.03</v>
+        <v>5846461.49</v>
       </c>
       <c r="AN5" t="n">
-        <v>458082156.64</v>
+        <v>462768262.53</v>
       </c>
       <c r="AO5" t="n">
-        <v>-313067360.49</v>
+        <v>328906126.35</v>
       </c>
       <c r="AP5" t="n">
-        <v>-94969188.91</v>
+        <v>-148637197.04</v>
       </c>
       <c r="AQ5" t="n">
         <v>0</v>
@@ -3543,25 +3543,25 @@
         <v>0</v>
       </c>
       <c r="AS5" t="n">
-        <v>-5724136695.81</v>
+        <v>-6703684327.47</v>
       </c>
       <c r="AT5" t="n">
-        <v>-173713008.1</v>
+        <v>-283302723.48</v>
       </c>
       <c r="AU5" t="n">
-        <v>-421464611.82</v>
+        <v>-532575439.75</v>
       </c>
       <c r="AV5" t="n">
-        <v>-5128959075.89</v>
+        <v>-5887806164.24</v>
       </c>
       <c r="AW5" t="n">
-        <v>5506038524.23</v>
+        <v>7181227650.86</v>
       </c>
       <c r="AX5" t="n">
-        <v>35594088.28</v>
+        <v>98061171.7</v>
       </c>
       <c r="AY5" t="n">
-        <v>5470444435.95</v>
+        <v>7083166479.16</v>
       </c>
     </row>
   </sheetData>
@@ -4166,197 +4166,197 @@
       </c>
       <c r="DN1" t="inlineStr">
         <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DO1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="DP1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="DQ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DR1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DS1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DT1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DU1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DV1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DW1" t="inlineStr">
+        <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>regularMarketChange</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>regularMarketDayRange</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EF1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EG1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="EH1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EI1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="EJ1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="EK1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="EL1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="EM1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EN1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EO1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="EP1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="EQ1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ER1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="ES1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="ET1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="EU1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="EV1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="EW1" t="inlineStr">
         <is>
           <t>cryptoTradeable</t>
         </is>
       </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
+      <c r="EX1" t="inlineStr">
         <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="ED1" t="inlineStr">
+      <c r="EY1" t="inlineStr">
+        <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="EZ1" t="inlineStr">
         <is>
           <t>longName</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EF1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EG1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="EH1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="EI1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EJ1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="EK1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EL1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EM1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="EN1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="EO1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="EP1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EQ1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="ER1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="ES1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="ET1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="EU1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EV1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EW1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EX1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EY1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="EZ1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
         </is>
       </c>
       <c r="FA1" t="inlineStr">
@@ -4461,34 +4461,34 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>5.57</v>
+        <v>5.08</v>
       </c>
       <c r="V2" t="n">
-        <v>5.58</v>
+        <v>5.04</v>
       </c>
       <c r="W2" t="n">
-        <v>5.48</v>
+        <v>4.92</v>
       </c>
       <c r="X2" t="n">
-        <v>5.62</v>
+        <v>5.09</v>
       </c>
       <c r="Y2" t="n">
-        <v>5.57</v>
+        <v>5.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>5.58</v>
+        <v>5.04</v>
       </c>
       <c r="AA2" t="n">
-        <v>5.48</v>
+        <v>4.92</v>
       </c>
       <c r="AB2" t="n">
-        <v>5.62</v>
+        <v>5.09</v>
       </c>
       <c r="AC2" t="n">
         <v>0.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.46</v>
+        <v>5.91</v>
       </c>
       <c r="AE2" t="n">
         <v>1758585600</v>
@@ -4500,34 +4500,34 @@
         <v>4.82</v>
       </c>
       <c r="AH2" t="n">
-        <v>0.28</v>
+        <v>0.219</v>
       </c>
       <c r="AI2" t="n">
-        <v>19.607141</v>
+        <v>18.142857</v>
       </c>
       <c r="AJ2" t="n">
-        <v>11.204081</v>
+        <v>10.367347</v>
       </c>
       <c r="AK2" t="n">
-        <v>10116700</v>
+        <v>13327871</v>
       </c>
       <c r="AL2" t="n">
-        <v>10116700</v>
+        <v>13327871</v>
       </c>
       <c r="AM2" t="n">
-        <v>13710964</v>
+        <v>11649442</v>
       </c>
       <c r="AN2" t="n">
-        <v>10173947</v>
+        <v>9574791</v>
       </c>
       <c r="AO2" t="n">
-        <v>10173947</v>
+        <v>9574791</v>
       </c>
       <c r="AP2" t="n">
-        <v>5.49</v>
+        <v>5.07</v>
       </c>
       <c r="AQ2" t="n">
-        <v>5.5</v>
+        <v>5.08</v>
       </c>
       <c r="AR2" t="n">
         <v>0</v>
@@ -4536,13 +4536,13 @@
         <v>0</v>
       </c>
       <c r="AT2" t="n">
-        <v>6868780032</v>
+        <v>6355811328</v>
       </c>
       <c r="AU2" t="n">
-        <v>6868779862</v>
+        <v>6355810874</v>
       </c>
       <c r="AV2" t="n">
-        <v>5.45</v>
+        <v>4.92</v>
       </c>
       <c r="AW2" t="n">
         <v>8.08</v>
@@ -4554,19 +4554,19 @@
         <v>2.092</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.7945893000000001</v>
+        <v>0.7352484</v>
       </c>
       <c r="BA2" t="n">
-        <v>6.194</v>
+        <v>5.8496</v>
       </c>
       <c r="BB2" t="n">
-        <v>6.7764</v>
+        <v>6.6821</v>
       </c>
       <c r="BC2" t="n">
         <v>0.18</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.032315977</v>
+        <v>0.035433073</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -4577,13 +4577,13 @@
         <v>0</v>
       </c>
       <c r="BG2" t="n">
-        <v>7788162560</v>
+        <v>7281687040</v>
       </c>
       <c r="BH2" t="n">
         <v>0.042969998</v>
       </c>
       <c r="BI2" t="n">
-        <v>604731768</v>
+        <v>600148782</v>
       </c>
       <c r="BJ2" t="n">
         <v>1251143873</v>
@@ -4592,7 +4592,7 @@
         <v>0.54517</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.056399997</v>
+        <v>0.05641</v>
       </c>
       <c r="BM2" t="n">
         <v>1251143873</v>
@@ -4601,7 +4601,7 @@
         <v>4.592</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.1955575</v>
+        <v>1.1062717</v>
       </c>
       <c r="BP2" t="n">
         <v>1767139200</v>
@@ -4633,16 +4633,16 @@
         <v>1428883200</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.901</v>
+        <v>0.842</v>
       </c>
       <c r="BZ2" t="n">
-        <v>11.896</v>
+        <v>11.123</v>
       </c>
       <c r="CA2" t="n">
-        <v>-0.046875</v>
+        <v>-0.08960575</v>
       </c>
       <c r="CB2" t="n">
-        <v>0.27697718</v>
+        <v>0.24487448</v>
       </c>
       <c r="CC2" t="n">
         <v>0.1</v>
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="CF2" t="n">
-        <v>5.49</v>
+        <v>5.08</v>
       </c>
       <c r="CG2" t="n">
         <v>7</v>
@@ -4773,146 +4773,146 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="DN2" t="b">
-        <v>0</v>
+      <c r="DN2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
       </c>
       <c r="DO2" t="n">
+        <v>1782111882</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>SHZ</t>
+        </is>
+      </c>
+      <c r="DQ2" t="inlineStr">
+        <is>
+          <t>finmb_75334081</t>
+        </is>
+      </c>
+      <c r="DR2" t="inlineStr">
+        <is>
+          <t>Asia/Shanghai</t>
+        </is>
+      </c>
+      <c r="DS2" t="inlineStr">
+        <is>
+          <t>CST</t>
+        </is>
+      </c>
+      <c r="DT2" t="n">
+        <v>28800000</v>
+      </c>
+      <c r="DU2" t="inlineStr">
+        <is>
+          <t>cn_market</t>
+        </is>
+      </c>
+      <c r="DV2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DX2" t="n">
         <v>1295314200000</v>
       </c>
-      <c r="DP2" t="n">
-        <v>-0.0800004</v>
-      </c>
-      <c r="DQ2" t="inlineStr">
-        <is>
-          <t>5.48 - 5.62</t>
-        </is>
-      </c>
-      <c r="DR2" t="inlineStr">
+      <c r="DY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DZ2" t="inlineStr">
+        <is>
+          <t>4.92 - 5.09</t>
+        </is>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>Shenzhen</t>
         </is>
       </c>
-      <c r="DS2" t="n">
-        <v>13710964</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.03999996</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0.0073394426</v>
-      </c>
-      <c r="DV2" t="inlineStr">
-        <is>
-          <t>5.45 - 8.08</t>
-        </is>
-      </c>
-      <c r="DW2" t="n">
-        <v>-2.5900002</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.32054457</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>-4.6875</v>
-      </c>
-      <c r="DZ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>-1.4362729</v>
-      </c>
       <c r="EB2" t="n">
-        <v>5.49</v>
-      </c>
-      <c r="EC2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="ED2" t="inlineStr">
+        <v>11649442</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.15999985</v>
+      </c>
+      <c r="ED2" t="n">
+        <v>0.032520294</v>
+      </c>
+      <c r="EE2" t="inlineStr">
+        <is>
+          <t>4.92 - 8.08</t>
+        </is>
+      </c>
+      <c r="EF2" t="n">
+        <v>-3</v>
+      </c>
+      <c r="EG2" t="n">
+        <v>-0.37128714</v>
+      </c>
+      <c r="EH2" t="n">
+        <v>-8.960575</v>
+      </c>
+      <c r="EI2" t="n">
+        <v>1651143540</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>1651233600</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="EO2" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="EP2" t="n">
+        <v>12.390244</v>
+      </c>
+      <c r="EQ2" t="n">
+        <v>-0.7695999</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>-0.13156454</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>-1.6020999</v>
+      </c>
+      <c r="ET2" t="n">
+        <v>-0.23975995</v>
+      </c>
+      <c r="EU2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>15</v>
+      </c>
+      <c r="EW2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EX2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="EY2" t="inlineStr">
+        <is>
+          <t>JIANGSU ASIA-PACIFIC LIGHT ALLO</t>
+        </is>
+      </c>
+      <c r="EZ2" t="inlineStr">
         <is>
           <t>Jiangsu Asia-Pacific Light Alloy Technology Co., Ltd.</t>
         </is>
-      </c>
-      <c r="EE2" t="n">
-        <v>1651143540</v>
-      </c>
-      <c r="EF2" t="n">
-        <v>1651233600</v>
-      </c>
-      <c r="EG2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>0.41</v>
-      </c>
-      <c r="EJ2" t="n">
-        <v>13.390244</v>
-      </c>
-      <c r="EK2" t="n">
-        <v>-0.704</v>
-      </c>
-      <c r="EL2" t="n">
-        <v>-0.11365838</v>
-      </c>
-      <c r="EM2" t="n">
-        <v>-1.2864003</v>
-      </c>
-      <c r="EN2" t="n">
-        <v>-0.18983535</v>
-      </c>
-      <c r="EO2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EP2" t="n">
-        <v>15</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>JIANGSU ASIA-PACIFIC LIGHT ALLO</t>
-        </is>
-      </c>
-      <c r="ER2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="ES2" t="n">
-        <v>1780038288</v>
-      </c>
-      <c r="ET2" t="inlineStr">
-        <is>
-          <t>SHZ</t>
-        </is>
-      </c>
-      <c r="EU2" t="inlineStr">
-        <is>
-          <t>finmb_75334081</t>
-        </is>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>Asia/Shanghai</t>
-        </is>
-      </c>
-      <c r="EW2" t="inlineStr">
-        <is>
-          <t>CST</t>
-        </is>
-      </c>
-      <c r="EX2" t="n">
-        <v>28800000</v>
-      </c>
-      <c r="EY2" t="inlineStr">
-        <is>
-          <t>cn_market</t>
-        </is>
-      </c>
-      <c r="EZ2" t="b">
-        <v>0</v>
       </c>
       <c r="FA2" t="inlineStr"/>
     </row>
